--- a/backend/seed_data/eleves_demo.xlsx
+++ b/backend/seed_data/eleves_demo.xlsx
@@ -516,10 +516,9 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stéphane</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Camille</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>julien.jean@exemple.fr</t>
@@ -538,15 +537,6 @@
           <t>07/01/2006 = 20 ans</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
           <t>X</t>
@@ -594,17 +584,6 @@
           <t>20/06/2021 = 5 ans</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -614,7 +593,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Milo</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -642,16 +621,6 @@
           <t>06/12/2010 = 15 ans</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>X</t>
@@ -694,16 +663,6 @@
           <t>08/11/2012 = 13 ans</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>X</t>
@@ -746,11 +705,6 @@
           <t>12/10/2015 = 10 ans</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>X</t>
@@ -766,8 +720,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>X</t>
@@ -782,7 +734,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Enzo</t>
+          <t>Lucie</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -810,15 +762,6 @@
           <t>04/11/2012 = 13 ans</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
           <t>X</t>
@@ -838,7 +781,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sacha</t>
+          <t>Margaux</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -866,16 +809,6 @@
           <t>01/03/2013 = 13 ans</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>X</t>
@@ -890,7 +823,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Léon</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -923,16 +856,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -945,7 +868,6 @@
           <t>Delphine</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>delphine.garcia@exemple.fr</t>
@@ -966,16 +888,6 @@
           <t>08/09/1970 = 56 ans</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>X</t>
@@ -990,10 +902,9 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nicolas</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>Juliette</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>pierre.legrand@exemple.fr</t>
@@ -1014,15 +925,6 @@
           <t>25/08/1980 = 46 ans</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1045,7 +947,6 @@
           <t>Elodie</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>elodie.lefebvre@exemple.fr</t>
@@ -1066,21 +967,11 @@
           <t>18/02/1990 = 36 ans</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1118,15 +1009,6 @@
           <t>09/12/2012 = 13 ans</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
           <t>X</t>
@@ -1146,7 +1028,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Eliott</t>
+          <t>Amandine</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1179,16 +1061,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1226,9 +1098,6 @@
           <t>23/03/2018 = 8 ans</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>X</t>
@@ -1239,12 +1108,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1282,11 +1145,6 @@
           <t>04/02/2015 = 11 ans</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>X</t>
@@ -1302,9 +1160,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1314,7 +1169,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>Coline</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1347,16 +1202,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1394,21 +1239,11 @@
           <t>18/06/2016 = 10 ans</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1446,9 +1281,6 @@
           <t>09/03/2017 = 9 ans</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>X</t>
@@ -1464,11 +1296,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1478,7 +1305,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Lola</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1506,16 +1333,6 @@
           <t>16/11/2011 = 14 ans</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>X</t>
@@ -1558,21 +1375,11 @@
           <t>22/09/2010 = 15 ans</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1615,16 +1422,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1667,16 +1464,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1689,7 +1476,6 @@
           <t>Isabelle</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>isabelle.perrot@exemple.fr</t>
@@ -1710,21 +1496,11 @@
           <t>24/06/2008 = 18 ans</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1762,21 +1538,11 @@
           <t>22/12/2015 = 10 ans</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1814,20 +1580,11 @@
           <t>22/09/2012 = 13 ans</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>X</t>
@@ -1845,7 +1602,6 @@
           <t>Julie</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>celine.duval@exemple.fr</t>
@@ -1866,17 +1622,6 @@
           <t>25/12/1966 = 59 ans</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1886,7 +1631,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Antoine</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1914,21 +1659,11 @@
           <t>11/03/2009 = 17 ans</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1966,21 +1701,11 @@
           <t>17/12/2016 = 9 ans</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2018,21 +1743,11 @@
           <t>05/02/2017 = 9 ans</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2042,7 +1757,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Arthur</t>
+          <t>Apolline</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2070,21 +1785,11 @@
           <t>01/03/2017 = 9 ans</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2094,7 +1799,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Léon</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2122,20 +1827,11 @@
           <t>13/07/2010 = 16 ans</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
           <t>X</t>
@@ -2150,7 +1846,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Baptiste</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2178,21 +1874,11 @@
           <t>26/06/2018 = 8 ans</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2202,7 +1888,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Malo</t>
+          <t>Margot</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2230,14 +1916,6 @@
           <t>11/07/2011 = 15 ans</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>X</t>
@@ -2290,11 +1968,6 @@
           <t>03/03/2015 = 11 ans</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>X</t>
@@ -2310,9 +1983,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2322,10 +1992,9 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Stéphane</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>Clara</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>julien.andre@exemple.fr</t>
@@ -2346,14 +2015,6 @@
           <t>18/06/2008 = 18 ans</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>X</t>
@@ -2381,7 +2042,6 @@
           <t>Sylvie</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>julien.michel@exemple.fr</t>
@@ -2402,21 +2062,11 @@
           <t>16/01/2004 = 22 ans</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2426,7 +2076,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Eliott</t>
+          <t>Justine</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2454,9 +2104,6 @@
           <t>10/07/2016 = 10 ans</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>X</t>
@@ -2467,7 +2114,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>X</t>
@@ -2478,9 +2124,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2490,7 +2133,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Pauline</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2518,14 +2161,6 @@
           <t>05/03/2012 = 14 ans</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>X</t>
@@ -2550,10 +2185,9 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Stéphane</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>Romane</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>nadia.petit@exemple.fr</t>
@@ -2574,20 +2208,11 @@
           <t>05/05/2008 = 18 ans</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
           <t>X</t>
@@ -2605,7 +2230,6 @@
           <t>Alice</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>alice.durand@exemple.fr</t>
@@ -2626,21 +2250,11 @@
           <t>07/10/1986 = 39 ans</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2650,7 +2264,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Robin</t>
+          <t>Lena</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2678,7 +2292,6 @@
           <t>23/07/2018 = 8 ans</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>X</t>
@@ -2689,18 +2302,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2738,21 +2344,11 @@
           <t>23/01/2015 = 11 ans</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2762,13 +2358,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>David</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>Mélanie</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>david.michel@exemple.fr</t>
+          <t>melanie.michel@exemple.fr</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2786,16 +2381,6 @@
           <t>03/09/1986 = 40 ans</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
         <is>
           <t>X</t>
@@ -2838,12 +2423,6 @@
           <t>02/11/2013 = 12 ans</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>X</t>
@@ -2859,8 +2438,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2898,25 +2475,16 @@
           <t>10/01/2015 = 11 ans</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2926,7 +2494,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nolan</t>
+          <t>Faustine</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2954,17 +2522,6 @@
           <t>02/02/2021 = 5 ans</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3002,9 +2559,6 @@
           <t>03/12/2017 = 8 ans</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>X</t>
@@ -3015,12 +2569,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3030,13 +2578,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Marc</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>Adèle</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>marc.perrin@exemple.fr</t>
+          <t>adele.perrin@exemple.fr</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3054,15 +2601,6 @@
           <t>10/05/2003 = 23 ans</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
           <t>X</t>
@@ -3110,21 +2648,11 @@
           <t>10/12/2012 = 13 ans</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3167,16 +2695,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3186,10 +2704,9 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fabien</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>Gabrielle</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>vincent.durand@exemple.fr</t>
@@ -3210,15 +2727,6 @@
           <t>15/12/1970 = 55 ans</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
           <t>X</t>
@@ -3266,7 +2774,6 @@
           <t>05/04/2018 = 8 ans</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>X</t>
@@ -3277,14 +2784,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3294,7 +2793,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Marceau</t>
+          <t>Valentine</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3327,16 +2826,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3374,14 +2863,6 @@
           <t>12/10/2012 = 13 ans</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>X</t>
@@ -3392,7 +2873,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3430,21 +2910,11 @@
           <t>06/06/2019 = 7 ans</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3482,16 +2952,6 @@
           <t>21/02/2012 = 14 ans</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
           <t>X</t>
@@ -3506,7 +2966,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Constance</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3549,14 +3009,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3594,21 +3046,11 @@
           <t>26/11/2015 = 10 ans</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3646,9 +3088,6 @@
           <t>16/07/2018 = 8 ans</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>X</t>
@@ -3659,12 +3098,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3677,7 +3110,6 @@
           <t>Nadia</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>nadia.garnier@exemple.fr</t>
@@ -3698,21 +3130,11 @@
           <t>13/11/1991 = 34 ans</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3725,7 +3147,6 @@
           <t>Delphine</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>delphine.garnier@exemple.fr</t>
@@ -3746,14 +3167,6 @@
           <t>17/07/1991 = 35 ans</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>X</t>
@@ -3806,21 +3219,11 @@
           <t>14/11/2010 = 15 ans</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3858,21 +3261,11 @@
           <t>25/10/2019 = 6 ans</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3910,21 +3303,11 @@
           <t>17/12/2019 = 6 ans</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3967,16 +3350,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3989,7 +3362,6 @@
           <t>Laurence</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>nicolas.vincent@exemple.fr</t>
@@ -4010,14 +3382,6 @@
           <t>17/10/1995 = 30 ans</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>X</t>
@@ -4028,7 +3392,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4041,7 +3404,6 @@
           <t>Sandrine</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>sandrine.lambert@exemple.fr</t>
@@ -4062,14 +3424,6 @@
           <t>06/07/1997 = 29 ans</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>X</t>
@@ -4080,7 +3434,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4090,7 +3443,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kylian</t>
+          <t>Noémie</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4118,21 +3471,11 @@
           <t>19/06/2017 = 9 ans</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4142,7 +3485,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Axel</t>
+          <t>Léonie</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4175,16 +3518,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4194,7 +3527,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Arthur</t>
+          <t>Céline</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4227,16 +3560,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4249,7 +3572,6 @@
           <t>Christelle</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>christelle.laurent@exemple.fr</t>
@@ -4270,14 +3592,6 @@
           <t>05/12/1976 = 49 ans</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>X</t>
@@ -4288,7 +3602,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4326,21 +3639,11 @@
           <t>06/04/2014 = 12 ans</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4383,20 +3686,11 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4439,16 +3733,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4458,7 +3742,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>Estelle</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4486,7 +3770,6 @@
           <t>01/09/2019 = 7 ans</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>X</t>
@@ -4497,14 +3780,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4542,21 +3817,11 @@
           <t>23/11/2015 = 10 ans</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4569,7 +3834,6 @@
           <t>Isabelle</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>isabelle.dumont@exemple.fr</t>
@@ -4590,21 +3854,11 @@
           <t>08/12/1975 = 50 ans</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4647,16 +3901,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4699,16 +3943,6 @@
           <t>X</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4718,13 +3952,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Karim</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>Ambre</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>karim.garnier@exemple.fr</t>
+          <t>ambre.garnier@exemple.fr</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4742,21 +3975,11 @@
           <t>07/11/1991 = 34 ans</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
